--- a/!!AgentWorkZone!!/需求.xlsx
+++ b/!!AgentWorkZone!!/需求.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25134" windowHeight="10407"/>
+    <workbookView windowWidth="19200" windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
   <si>
     <t>装备</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>涡轮棒棒糖发射器</t>
+  </si>
+  <si>
+    <t>√</t>
   </si>
   <si>
     <t>薄荷拐杖糖</t>
@@ -1481,10 +1484,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:M36"/>
-  <sheetFormatPr defaultColWidth="8.88135593220339" defaultRowHeight="13.05"/>
+  <sheetFormatPr defaultColWidth="8.88333333333333" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="23.0762711864407" customWidth="1"/>
-    <col min="5" max="5" width="13.7542372881356" customWidth="1"/>
+    <col min="2" max="2" width="23.075" customWidth="1"/>
+    <col min="5" max="5" width="13.7583333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -1635,7 +1638,9 @@
       <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -1650,9 +1655,11 @@
     <row r="11" spans="1:13">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -1679,12 +1686,12 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" ht="13.75" spans="1:13">
+    <row r="13" spans="1:13">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -1698,10 +1705,10 @@
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" ht="13.75" spans="1:13">
+    <row r="14" spans="1:13">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -1715,10 +1722,10 @@
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
     </row>
-    <row r="15" ht="13.75" spans="1:13">
+    <row r="15" spans="1:13">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -1732,10 +1739,10 @@
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
     </row>
-    <row r="16" ht="13.75" spans="1:13">
+    <row r="16" spans="1:13">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -1749,10 +1756,10 @@
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
     </row>
-    <row r="17" ht="13.75" spans="1:13">
+    <row r="17" spans="1:13">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -1783,12 +1790,14 @@
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
@@ -1817,10 +1826,10 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -1837,7 +1846,7 @@
     <row r="22" spans="1:13">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -1854,7 +1863,7 @@
     <row r="23" spans="1:13">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -1885,10 +1894,10 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -1905,35 +1914,35 @@
     <row r="26" spans="1:13">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="1"/>
       <c r="B27" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="1"/>
       <c r="B28" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="B30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" ht="13" customHeight="1" spans="1:13">
       <c r="B31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1943,26 +1952,32 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="1"/>
-    </row>
-    <row r="34" ht="13.75" spans="1:3">
+        <v>34</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" s="1"/>
       <c r="B34" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="1"/>
+        <v>35</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="1"/>
       <c r="B35" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C35" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="1"/>
